--- a/rules/CORE-000790/positive/01/data/unit-test-coreid-FB2505-positive.xlsx
+++ b/rules/CORE-000790/positive/01/data/unit-test-coreid-FB2505-positive.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Repos\verisian\core-contributor\rules\CORE-000790\positive\01\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\els_janssens\CORE\Rule_Authoring\core-contributor\rules\CORE-000790\positive\01\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2062FB6-FEDF-42B6-BE36-57886CDCDF8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AC9BB58-76FA-4310-A7B0-86846558460C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Library" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="151">
   <si>
     <t>Product</t>
   </si>
@@ -229,9 +229,6 @@
     <t>DM</t>
   </si>
   <si>
-    <t>015246-076-0003-00003</t>
-  </si>
-  <si>
     <t>076000300003</t>
   </si>
   <si>
@@ -274,9 +271,6 @@
     <t>BRA</t>
   </si>
   <si>
-    <t>015246-300-0004-00002</t>
-  </si>
-  <si>
     <t>300000400002</t>
   </si>
   <si>
@@ -313,9 +307,6 @@
     <t>GRC</t>
   </si>
   <si>
-    <t>015246-999-0004-9999</t>
-  </si>
-  <si>
     <t>99900049999</t>
   </si>
   <si>
@@ -337,18 +328,9 @@
     <t>Not Treated</t>
   </si>
   <si>
-    <t>015246-076-0003-00004</t>
-  </si>
-  <si>
     <t>RANDOM</t>
   </si>
   <si>
-    <t>015246-300-0004-00012</t>
-  </si>
-  <si>
-    <t>015246-999-0004-1000</t>
-  </si>
-  <si>
     <t>EXSEQ</t>
   </si>
   <si>
@@ -476,6 +458,24 @@
   </si>
   <si>
     <t>A2-20110125</t>
+  </si>
+  <si>
+    <t>123</t>
+  </si>
+  <si>
+    <t>124</t>
+  </si>
+  <si>
+    <t>125</t>
+  </si>
+  <si>
+    <t>126</t>
+  </si>
+  <si>
+    <t>127</t>
+  </si>
+  <si>
+    <t>128</t>
   </si>
 </sst>
 </file>
@@ -484,7 +484,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0;[Red]0"/>
-    <numFmt numFmtId="166" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -582,7 +582,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -623,10 +623,7 @@
     <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -989,7 +986,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:AA10"/>
+  <dimension ref="A1:AA9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:27" ht="30" x14ac:dyDescent="0.25">
@@ -1332,71 +1329,71 @@
         <v>67</v>
       </c>
       <c r="C5" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="D5" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="E5" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="E5" s="7" t="s">
+      <c r="F5" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="F5" s="7" t="s">
+      <c r="G5" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="H5" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="I5" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="G5" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="H5" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="I5" s="7" t="s">
+      <c r="J5" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="J5" s="7" t="s">
-        <v>73</v>
-      </c>
       <c r="K5" s="8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="L5" s="8"/>
       <c r="M5" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="N5" s="7" t="s">
         <v>74</v>
-      </c>
-      <c r="N5" s="7" t="s">
-        <v>75</v>
       </c>
       <c r="O5" s="9">
         <v>78</v>
       </c>
       <c r="P5" s="8"/>
       <c r="Q5" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="R5" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="R5" s="7" t="s">
+      <c r="S5" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="S5" s="7" t="s">
+      <c r="T5" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="T5" s="7" t="s">
+      <c r="U5" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="U5" s="8" t="s">
+      <c r="V5" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="V5" s="8" t="s">
-        <v>81</v>
-      </c>
       <c r="W5" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="X5" s="8" t="s">
         <v>80</v>
-      </c>
-      <c r="X5" s="8" t="s">
-        <v>81</v>
       </c>
       <c r="Y5" s="8"/>
       <c r="Z5" s="7"/>
       <c r="AA5" s="7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="6" spans="1:27" ht="60" x14ac:dyDescent="0.25">
@@ -1407,73 +1404,73 @@
         <v>67</v>
       </c>
       <c r="C6" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="E6" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="F6" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="E6" s="7" t="s">
+      <c r="G6" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="H6" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="I6" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="F6" s="7" t="s">
+      <c r="J6" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="G6" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="H6" s="7" t="s">
+      <c r="K6" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="I6" s="7" t="s">
+      <c r="L6" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="J6" s="7" t="s">
+      <c r="M6" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="K6" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="L6" s="8" t="s">
+      <c r="N6" s="7" t="s">
         <v>89</v>
-      </c>
-      <c r="M6" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="N6" s="7" t="s">
-        <v>91</v>
       </c>
       <c r="O6" s="9">
         <v>70</v>
       </c>
       <c r="P6" s="8"/>
       <c r="Q6" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="R6" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="R6" s="7" t="s">
+      <c r="S6" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="S6" s="7" t="s">
-        <v>78</v>
-      </c>
       <c r="T6" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="U6" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="V6" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="U6" s="8" t="s">
-        <v>93</v>
-      </c>
-      <c r="V6" s="8" t="s">
-        <v>94</v>
-      </c>
       <c r="W6" s="8" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="X6" s="8" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="Y6" s="8"/>
       <c r="Z6" s="7"/>
       <c r="AA6" s="7" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="7" spans="1:27" ht="60" x14ac:dyDescent="0.25">
@@ -1484,73 +1481,73 @@
         <v>67</v>
       </c>
       <c r="C7" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="H7" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="I7" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="J7" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="K7" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="L7" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="D7" s="7" t="s">
-        <v>97</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="F7" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="G7" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="H7" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="I7" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="J7" s="7" t="s">
+      <c r="M7" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="K7" s="8" t="s">
-        <v>98</v>
-      </c>
-      <c r="L7" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="M7" s="7" t="s">
-        <v>90</v>
-      </c>
       <c r="N7" s="7" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="O7" s="9">
         <v>71</v>
       </c>
       <c r="P7" s="8"/>
       <c r="Q7" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="R7" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="R7" s="7" t="s">
+      <c r="S7" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="S7" s="7" t="s">
-        <v>78</v>
-      </c>
       <c r="T7" s="7" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="U7" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="V7" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="W7" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="X7" s="8" t="s">
         <v>100</v>
-      </c>
-      <c r="V7" s="8" t="s">
-        <v>101</v>
-      </c>
-      <c r="W7" s="8" t="s">
-        <v>102</v>
-      </c>
-      <c r="X7" s="8" t="s">
-        <v>103</v>
       </c>
       <c r="Y7" s="8"/>
       <c r="Z7" s="7"/>
       <c r="AA7" s="7" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="8" spans="1:27" ht="45" x14ac:dyDescent="0.25">
@@ -1560,72 +1557,72 @@
       <c r="B8" t="s">
         <v>67</v>
       </c>
-      <c r="C8" s="17" t="s">
-        <v>104</v>
+      <c r="C8" s="7" t="s">
+        <v>148</v>
       </c>
       <c r="D8" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="E8" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="E8" s="7" t="s">
+      <c r="F8" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="F8" s="7" t="s">
+      <c r="G8" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="H8" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="I8" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="G8" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="H8" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="I8" s="7" t="s">
+      <c r="J8" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="J8" s="7" t="s">
-        <v>73</v>
-      </c>
       <c r="K8" s="8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="L8" s="8"/>
       <c r="M8" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="N8" s="7" t="s">
         <v>74</v>
-      </c>
-      <c r="N8" s="7" t="s">
-        <v>75</v>
       </c>
       <c r="O8" s="9">
         <v>78</v>
       </c>
       <c r="P8" s="8"/>
       <c r="Q8" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="R8" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="R8" s="7" t="s">
+      <c r="S8" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="S8" s="7" t="s">
+      <c r="T8" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="T8" s="7" t="s">
-        <v>79</v>
-      </c>
       <c r="U8" s="8" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="V8" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="W8" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="W8" s="8" t="s">
-        <v>105</v>
-      </c>
       <c r="X8" s="8" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="Y8" s="8"/>
       <c r="Z8" s="7"/>
       <c r="AA8" s="7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="9" spans="1:27" ht="60" x14ac:dyDescent="0.25">
@@ -1635,151 +1632,72 @@
       <c r="B9" t="s">
         <v>67</v>
       </c>
-      <c r="C9" s="17" t="s">
-        <v>106</v>
+      <c r="C9" s="7" t="s">
+        <v>149</v>
       </c>
       <c r="D9" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="F9" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="E9" s="7" t="s">
+      <c r="G9" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="H9" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="I9" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="F9" s="7" t="s">
+      <c r="J9" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="G9" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="H9" s="7" t="s">
+      <c r="K9" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="I9" s="7" t="s">
+      <c r="L9" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="J9" s="7" t="s">
+      <c r="M9" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="K9" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="L9" s="8" t="s">
+      <c r="N9" s="7" t="s">
         <v>89</v>
-      </c>
-      <c r="M9" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="N9" s="7" t="s">
-        <v>91</v>
       </c>
       <c r="O9" s="9">
         <v>70</v>
       </c>
       <c r="P9" s="8"/>
       <c r="Q9" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="R9" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="R9" s="7" t="s">
+      <c r="S9" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="S9" s="7" t="s">
-        <v>78</v>
-      </c>
       <c r="T9" s="7" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="U9" s="8" t="s">
-        <v>100</v>
-      </c>
-      <c r="V9" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="V9" s="8"/>
+      <c r="W9" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="W9" s="8" t="s">
-        <v>105</v>
-      </c>
       <c r="X9" s="8" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="Y9" s="8"/>
       <c r="Z9" s="7"/>
       <c r="AA9" s="7" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="10" spans="1:27" ht="60" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>66</v>
-      </c>
-      <c r="B10" t="s">
-        <v>67</v>
-      </c>
-      <c r="C10" s="17" t="s">
-        <v>107</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>97</v>
-      </c>
-      <c r="E10" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="F10" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="G10" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="H10" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="I10" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="J10" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="K10" s="8" t="s">
-        <v>98</v>
-      </c>
-      <c r="L10" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="M10" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="N10" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="O10" s="9">
-        <v>71</v>
-      </c>
-      <c r="P10" s="8"/>
-      <c r="Q10" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="R10" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="S10" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="T10" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="U10" s="8" t="s">
-        <v>100</v>
-      </c>
-      <c r="V10" s="8" t="s">
-        <v>101</v>
-      </c>
-      <c r="W10" s="8" t="s">
-        <v>105</v>
-      </c>
-      <c r="X10" s="8" t="s">
-        <v>101</v>
-      </c>
-      <c r="Y10" s="8"/>
-      <c r="Z10" s="7"/>
-      <c r="AA10" s="7" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
   </sheetData>
@@ -1803,49 +1721,49 @@
         <v>12</v>
       </c>
       <c r="D1" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="G1" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="H1" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="I1" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="J1" s="10" t="s">
         <v>108</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="K1" s="10" t="s">
         <v>109</v>
       </c>
-      <c r="F1" s="10" t="s">
+      <c r="L1" s="10" t="s">
         <v>110</v>
       </c>
-      <c r="G1" s="10" t="s">
+      <c r="M1" s="11" t="s">
         <v>111</v>
       </c>
-      <c r="H1" s="10" t="s">
+      <c r="N1" s="11" t="s">
         <v>112</v>
       </c>
-      <c r="I1" s="10" t="s">
+      <c r="O1" s="10" t="s">
         <v>113</v>
       </c>
-      <c r="J1" s="10" t="s">
+      <c r="P1" s="10" t="s">
         <v>114</v>
       </c>
-      <c r="K1" s="10" t="s">
+      <c r="Q1" s="10" t="s">
         <v>115</v>
       </c>
-      <c r="L1" s="10" t="s">
+      <c r="R1" s="10" t="s">
         <v>116</v>
-      </c>
-      <c r="M1" s="11" t="s">
-        <v>117</v>
-      </c>
-      <c r="N1" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="O1" s="10" t="s">
-        <v>119</v>
-      </c>
-      <c r="P1" s="10" t="s">
-        <v>120</v>
-      </c>
-      <c r="Q1" s="10" t="s">
-        <v>121</v>
-      </c>
-      <c r="R1" s="10" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="2" spans="1:18" ht="75" x14ac:dyDescent="0.25">
@@ -1859,49 +1777,49 @@
         <v>39</v>
       </c>
       <c r="D2" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="E2" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="F2" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="G2" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="H2" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="I2" s="12" t="s">
+        <v>122</v>
+      </c>
+      <c r="J2" s="12" t="s">
         <v>123</v>
       </c>
-      <c r="E2" s="12" t="s">
+      <c r="K2" s="12" t="s">
         <v>124</v>
       </c>
-      <c r="F2" s="12" t="s">
+      <c r="L2" s="12" t="s">
         <v>125</v>
       </c>
-      <c r="G2" s="12" t="s">
+      <c r="M2" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="N2" s="12" t="s">
+        <v>122</v>
+      </c>
+      <c r="O2" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="H2" s="12" t="s">
+      <c r="P2" s="12" t="s">
         <v>127</v>
       </c>
-      <c r="I2" s="12" t="s">
+      <c r="Q2" s="12" t="s">
         <v>128</v>
       </c>
-      <c r="J2" s="12" t="s">
+      <c r="R2" s="12" t="s">
         <v>129</v>
-      </c>
-      <c r="K2" s="12" t="s">
-        <v>130</v>
-      </c>
-      <c r="L2" s="12" t="s">
-        <v>131</v>
-      </c>
-      <c r="M2" s="12" t="s">
-        <v>126</v>
-      </c>
-      <c r="N2" s="12" t="s">
-        <v>128</v>
-      </c>
-      <c r="O2" s="12" t="s">
-        <v>132</v>
-      </c>
-      <c r="P2" s="12" t="s">
-        <v>133</v>
-      </c>
-      <c r="Q2" s="12" t="s">
-        <v>134</v>
-      </c>
-      <c r="R2" s="12" t="s">
-        <v>135</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
@@ -2016,45 +1934,45 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:18" ht="45" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>66</v>
       </c>
       <c r="B5" t="s">
-        <v>136</v>
-      </c>
-      <c r="C5" s="17" t="s">
-        <v>104</v>
+        <v>130</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>147</v>
       </c>
       <c r="D5">
         <v>1</v>
       </c>
       <c r="E5" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="F5" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="G5">
         <v>3</v>
       </c>
       <c r="I5" s="13" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="J5" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="K5" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="L5" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="M5" s="14">
         <v>0.1</v>
       </c>
       <c r="N5" s="15" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="O5" s="16">
         <v>40557</v>
@@ -2069,39 +1987,39 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:18" ht="45" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>66</v>
       </c>
       <c r="B6" t="s">
-        <v>136</v>
-      </c>
-      <c r="C6" s="17" t="s">
-        <v>106</v>
+        <v>130</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>148</v>
       </c>
       <c r="D6">
         <v>1</v>
       </c>
       <c r="E6" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="F6" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="G6">
         <v>500</v>
       </c>
       <c r="I6" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="J6" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="K6" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="L6" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="O6" s="16">
         <v>40557</v>
@@ -2116,39 +2034,39 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:18" ht="45" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>66</v>
       </c>
       <c r="B7" t="s">
-        <v>136</v>
-      </c>
-      <c r="C7" s="17" t="s">
-        <v>107</v>
+        <v>130</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>150</v>
       </c>
       <c r="D7">
         <v>2</v>
       </c>
       <c r="E7" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="F7" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="G7">
         <v>500</v>
       </c>
       <c r="I7" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="J7" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="K7" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="L7" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="O7" s="16">
         <v>40568</v>
